--- a/src/semeio/fmudesign/examples/fmudesign_ex_onebyone.xlsx
+++ b/src/semeio/fmudesign/examples/fmudesign_ex_onebyone.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/LEVJE/dev_komodo/semeio/src/semeio/fmudesign/examples/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA5C94-6A92-AA42-B57D-B44BBB46BAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34560" windowHeight="20520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="general_input" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="designinput" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="defaultvalues" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="INFO" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="general_input" sheetId="1" r:id="rId1"/>
+    <sheet name="designinput" sheetId="2" r:id="rId2"/>
+    <sheet name="defaultvalues" sheetId="3" r:id="rId3"/>
+    <sheet name="INFO" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,12 +28,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author> </author>
+    <author/>
   </authors>
   <commentList>
-    <comment ref="B2" authorId="0">
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -38,11 +43,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Default number of realisations per sensitivity/scenario. Typically &gt; 1 for repeating seeds.</t>
+          <t>Default number of realisations per sensitivity/scenario. Typically &gt; 1 for repeating seeds.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -52,14 +57,14 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Alternatives:
+          <t>Alternatives:
 - default: means using RMS_SEED 1000-1001-1002-1003-…
 - None: RMS_SEED is not added as parameter in spreadsheet
 - filname for filw with list of seeds (one column)</t>
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -70,14 +75,54 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Advanced option to include sampled background parameters (see documentation).
-Alternatives:
-- None (no sampled background parameters)
-- name of sheet in current workbook containing distributions for background parameters
-- name of external file with background parameters (suffix .xlsx or .csv) Must be readable as pandas data frame with parameter names as column headers. Path is relative to where fmudesign is run from.</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Alternatives:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- None (no sampled background parameters)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- name of sheet in current workbook containing distributions for background parameters
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- name of external file with background parameters (suffix .xlsx or .csv) Must be readable as pandas data frame with parameter names as column headers. Path is relative to where fmudesign is run from.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -88,9 +133,75 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">Set RNG seed for "dist" sensitivities
-Alternatives:
-- Integer (e.g. 395830)
-- None (leads to non-reproducible analysis)</t>
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Alternatives:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">- Integer (e.g. 395830)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>- None (leads to non-reproducible analysis)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{FFAC18C8-77A6-1643-8CBA-DC30EF1AF3FE}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Controls how parameter setup changes affect Monte Carlo samples:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">  -  joint  (default): Adding, removing, or reordering parameters may change samples for other parameters.
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">  -  independent : Samples for unchanged parameters and correlation groups stay the same, provided neither distribution seed nor the sample size changes.</t>
         </r>
       </text>
     </comment>
@@ -99,12 +210,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author> </author>
+    <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -118,14 +229,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">one</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>one</t>
         </r>
         <r>
           <rPr>
@@ -139,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -149,20 +260,20 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Optional columns in grey text.
+          <t>Optional columns in grey text.
 Numreal: number of realisations per sensitivity/scenario.
 Overwrites number of realisations from '</t>
         </r>
         <r>
           <rPr>
-            <i val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">repeats</t>
+            <i/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>repeats</t>
         </r>
         <r>
           <rPr>
@@ -176,7 +287,7 @@
         </r>
         <r>
           <rPr>
-            <i val="true"/>
+            <i/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -193,11 +304,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">sheet.</t>
+          <t>sheet.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -207,7 +318,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">seed:</t>
+          <t>seed:</t>
         </r>
         <r>
           <rPr>
@@ -222,14 +333,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">scenario:</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>scenario:</t>
         </r>
         <r>
           <rPr>
@@ -244,14 +355,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">dist:</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>dist:</t>
         </r>
         <r>
           <rPr>
@@ -266,14 +377,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">ref:</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>ref:</t>
         </r>
         <r>
           <rPr>
@@ -289,14 +400,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">background:</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>background:</t>
         </r>
         <r>
           <rPr>
@@ -311,7 +422,7 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
+            <b/>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="Tahoma"/>
@@ -328,11 +439,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">parameter values read from an external file, typically createed in another software</t>
+          <t>parameter values read from an external file, typically createed in another software</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -342,11 +453,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">name of first alternative scenario. Will show up in SENSCASE column in design matrix</t>
+          <t>name of first alternative scenario. Will show up in SENSCASE column in design matrix</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -356,11 +467,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">parameter value(s) for first alternative scenario</t>
+          <t>parameter value(s) for first alternative scenario</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -370,11 +481,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">name of 2nd alternative scenario. Will show up in SENSCASE column in design matrix</t>
+          <t>name of 2nd alternative scenario. Will show up in SENSCASE column in design matrix</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -384,11 +495,11 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">parameter value(s) for first alternative scenario</t>
+          <t>parameter value(s) for first alternative scenario</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -403,14 +514,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">norm</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>norm</t>
         </r>
         <r>
           <rPr>
@@ -425,14 +536,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">norm</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>norm</t>
         </r>
         <r>
           <rPr>
@@ -447,14 +558,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">unif</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>unif</t>
         </r>
         <r>
           <rPr>
@@ -469,14 +580,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">logunif</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>logunif</t>
         </r>
         <r>
           <rPr>
@@ -490,14 +601,14 @@
         </r>
         <r>
           <rPr>
-            <i val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">output</t>
+            <i/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>output</t>
         </r>
         <r>
           <rPr>
@@ -512,14 +623,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">triang</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>triang</t>
         </r>
         <r>
           <rPr>
@@ -534,14 +645,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">pert</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>pert</t>
         </r>
         <r>
           <rPr>
@@ -556,14 +667,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">pert</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>pert</t>
         </r>
         <r>
           <rPr>
@@ -578,14 +689,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">beta</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>beta</t>
         </r>
         <r>
           <rPr>
@@ -600,14 +711,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">beta</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>beta</t>
         </r>
         <r>
           <rPr>
@@ -622,14 +733,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">discrete</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>discrete</t>
         </r>
         <r>
           <rPr>
@@ -644,14 +755,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">logn</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>logn</t>
         </r>
         <r>
           <rPr>
@@ -665,14 +776,14 @@
         </r>
         <r>
           <rPr>
-            <i val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">logarithm</t>
+            <i/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>logarithm</t>
         </r>
         <r>
           <rPr>
@@ -687,14 +798,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">const</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>const</t>
         </r>
         <r>
           <rPr>
@@ -709,14 +820,14 @@
         </r>
         <r>
           <rPr>
-            <b val="true"/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Bold</t>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Bold</t>
         </r>
         <r>
           <rPr>
@@ -730,7 +841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -740,12 +851,12 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Optional column:
+          <t>Optional column:
 For sensitivities of type dist. Will round output numbers to this number of decimals.</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -755,12 +866,12 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Optional column:
+          <t>Optional column:
 For sensitivities of type dist. Name of sheet with correlation matrix.</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -770,7 +881,7 @@
             <family val="2"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Optional column:
+          <t>Optional column:
 For sensitivities of type extern. Name of file to read parameters from.</t>
         </r>
       </text>
@@ -780,193 +891,196 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
-  <si>
-    <t xml:space="preserve">designtype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">onebyone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">repeats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rms_seeds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">background</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distribution_seed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sensname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">numreal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">param_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senscase1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">senscase2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_param1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_param2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_param3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist_param4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corr_sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extern_file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rms_seed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">faults</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FAULT_POSITION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">east</t>
-  </si>
-  <si>
-    <t xml:space="preserve">west</t>
-  </si>
-  <si>
-    <t xml:space="preserve">velmodel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DC_MODEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alternative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hum2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contacts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shallow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OWC3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">multz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MULTZ_ILE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logunif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default_values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RMS_SEED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAM3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This file is an example for configuration of design matrix for one-by-one sensitivities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and contains the set up for the three mandatory pages. For more advanced set ups consult the documentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edit the file to contain your sensitivities and save to ert/input/distributions</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
+  <si>
+    <t>designtype</t>
+  </si>
+  <si>
+    <t>onebyone</t>
+  </si>
+  <si>
+    <t>repeats</t>
+  </si>
+  <si>
+    <t>rms_seeds</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>background</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>distribution_seed</t>
+  </si>
+  <si>
+    <t>sensname</t>
+  </si>
+  <si>
+    <t>numreal</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>param_name</t>
+  </si>
+  <si>
+    <t>senscase1</t>
+  </si>
+  <si>
+    <t>value1</t>
+  </si>
+  <si>
+    <t>senscase2</t>
+  </si>
+  <si>
+    <t>value2</t>
+  </si>
+  <si>
+    <t>dist_name</t>
+  </si>
+  <si>
+    <t>dist_param1</t>
+  </si>
+  <si>
+    <t>dist_param2</t>
+  </si>
+  <si>
+    <t>dist_param3</t>
+  </si>
+  <si>
+    <t>dist_param4</t>
+  </si>
+  <si>
+    <t>decimals</t>
+  </si>
+  <si>
+    <t>corr_sheet</t>
+  </si>
+  <si>
+    <t>extern_file</t>
+  </si>
+  <si>
+    <t>rms_seed</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>faults</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>FAULT_POSITION</t>
+  </si>
+  <si>
+    <t>east</t>
+  </si>
+  <si>
+    <t>west</t>
+  </si>
+  <si>
+    <t>velmodel</t>
+  </si>
+  <si>
+    <t>DC_MODEL</t>
+  </si>
+  <si>
+    <t>alternative</t>
+  </si>
+  <si>
+    <t>hum2</t>
+  </si>
+  <si>
+    <t>contacts</t>
+  </si>
+  <si>
+    <t>OWC1</t>
+  </si>
+  <si>
+    <t>shallow</t>
+  </si>
+  <si>
+    <t>deep</t>
+  </si>
+  <si>
+    <t>OWC2</t>
+  </si>
+  <si>
+    <t>OWC3</t>
+  </si>
+  <si>
+    <t>multz</t>
+  </si>
+  <si>
+    <t>dist</t>
+  </si>
+  <si>
+    <t>MULTZ_ILE</t>
+  </si>
+  <si>
+    <t>logunif</t>
+  </si>
+  <si>
+    <t>default_values</t>
+  </si>
+  <si>
+    <t>RMS_SEED</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>PARAM1</t>
+  </si>
+  <si>
+    <t>PARAM2</t>
+  </si>
+  <si>
+    <t>PARAM3</t>
+  </si>
+  <si>
+    <t>This file is an example for configuration of design matrix for one-by-one sensitivities</t>
+  </si>
+  <si>
+    <t>and contains the set up for the three mandatory pages. For more advanced set ups consult the documentation</t>
+  </si>
+  <si>
+    <t>Edit the file to contain your sensitivities and save to ert/input/distributions</t>
   </si>
   <si>
     <t xml:space="preserve">Run with command from terminal window: </t>
   </si>
   <si>
-    <t xml:space="preserve">fmudesign design_input_template.xlsx output_design_matrix.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel files can be edited on Linux using</t>
-  </si>
-  <si>
-    <t xml:space="preserve">oocalc filename.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note that point is used as a decimal separator in the set up, while comma will separate different values for discrete distributions</t>
+    <t>fmudesign design_input_template.xlsx output_design_matrix.xlsx</t>
+  </si>
+  <si>
+    <t>Excel files can be edited on Linux using</t>
+  </si>
+  <si>
+    <t>oocalc filename.xlsx</t>
+  </si>
+  <si>
+    <t>Note that point is used as a decimal separator in the set up, while comma will separate different values for discrete distributions</t>
+  </si>
+  <si>
+    <t>seed_strategy</t>
+  </si>
+  <si>
+    <t>joint</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -975,22 +1089,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1005,7 +1104,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF808080"/>
       <name val="Calibri"/>
@@ -1013,7 +1112,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
@@ -1021,12 +1120,19 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1062,313 +1168,308 @@
     </fill>
   </fills>
   <borders count="13">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="46">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1427,24 +1528,352 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.13"/>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1452,15 +1881,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1476,7 +1905,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1484,42 +1913,42 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="5" width="6.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="4" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="5" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="6" width="10.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="6" width="10.85"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="3" width="8.33203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="3" customWidth="1"/>
+    <col min="11" max="13" width="11.83203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.83203125" style="5" customWidth="1"/>
+    <col min="15" max="15" width="10.5" style="6" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1569,7 +1998,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>24</v>
       </c>
@@ -1591,7 +2020,7 @@
       <c r="O2" s="23"/>
       <c r="P2" s="23"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
         <v>26</v>
       </c>
@@ -1605,13 +2034,13 @@
       <c r="E3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="25" t="n">
+      <c r="F3" s="25">
         <v>-1</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="28" t="n">
+      <c r="H3" s="28">
         <v>1</v>
       </c>
       <c r="I3" s="27"/>
@@ -1623,7 +2052,7 @@
       <c r="O3" s="30"/>
       <c r="P3" s="30"/>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="31" t="s">
         <v>31</v>
       </c>
@@ -1651,7 +2080,7 @@
       <c r="O4" s="37"/>
       <c r="P4" s="37"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="24" t="s">
         <v>35</v>
       </c>
@@ -1665,13 +2094,13 @@
       <c r="E5" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="25">
         <v>2600</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="28">
         <v>2700</v>
       </c>
       <c r="I5" s="27"/>
@@ -1683,7 +2112,7 @@
       <c r="O5" s="30"/>
       <c r="P5" s="30"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="24"/>
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
@@ -1691,11 +2120,11 @@
         <v>39</v>
       </c>
       <c r="E6" s="27"/>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="25">
         <v>2700</v>
       </c>
       <c r="G6" s="25"/>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="28">
         <v>2800</v>
       </c>
       <c r="I6" s="27"/>
@@ -1707,7 +2136,7 @@
       <c r="O6" s="30"/>
       <c r="P6" s="30"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="24"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
@@ -1715,11 +2144,11 @@
         <v>40</v>
       </c>
       <c r="E7" s="27"/>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="25">
         <v>2800</v>
       </c>
       <c r="G7" s="25"/>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="28">
         <v>2900</v>
       </c>
       <c r="I7" s="27"/>
@@ -1731,11 +2160,11 @@
       <c r="O7" s="30"/>
       <c r="P7" s="30"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="39" t="n">
+      <c r="B8" s="39">
         <v>20</v>
       </c>
       <c r="C8" s="39" t="s">
@@ -1751,10 +2180,10 @@
       <c r="I8" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="39" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="K8" s="39" t="n">
+      <c r="J8" s="39">
+        <v>1E-4</v>
+      </c>
+      <c r="K8" s="39">
         <v>1</v>
       </c>
       <c r="L8" s="39"/>
@@ -1764,30 +2193,22 @@
       <c r="P8" s="43"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.28"/>
+    <col min="1" max="1" width="16.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -1795,148 +2216,135 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>2650</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="1">
         <v>2750</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="1">
         <v>2850</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="1">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>